--- a/docs/2026-계획안-견적서/2026_바이브코딩_특강및경진대회_원가계산서.xlsx
+++ b/docs/2026-계획안-견적서/2026_바이브코딩_특강및경진대회_원가계산서.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="인건비(전문가)" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="일반경비" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="참고(증액 검토)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="강사수당 지급기준" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -77,7 +78,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -97,6 +98,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="0017365D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4F7FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -126,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -205,6 +216,27 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -629,10 +661,10 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>3500000</v>
+        <v>3250000</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>0.38500000385</v>
+        <v>0.3575000035750001</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -675,10 +707,10 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>176000</v>
+        <v>256500</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>0.0193600001936</v>
+        <v>0.02821500028215</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -687,7 +719,7 @@
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>(3) = {(1) + (2)} × 2.0%   지방계약법 시행규칙 제8조제1항제14호(8% 이내)</t>
+          <t>(3) = {(1) + (2)} × 3.0%   지방계약법 시행규칙 제8조제1항제14호(8% 이내)</t>
         </is>
       </c>
     </row>
@@ -698,10 +730,10 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>114909</v>
+        <v>284409</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>0.0126399901263999</v>
+        <v>0.0312849903128499</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -710,7 +742,7 @@
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>(4) = {(1) + (2) + (3)} × 1.28%   지방계약법 시행규칙 제8조제2항제4호(10% 이내)</t>
+          <t>(4) = {(1) + (2) + (3)} × 3.23%   지방계약법 시행규칙 제8조제2항제4호(10% 이내)</t>
         </is>
       </c>
     </row>
@@ -786,7 +818,7 @@
     <row r="12" ht="42" customHeight="1">
       <c r="A12" s="22" t="inlineStr">
         <is>
-          <t>※ 2025년 원가계산서는 일반관리비 6% · 이윤 10%를 적용하였으나, 본 과업은 시상금(2,500,000원)과 AI 코딩 도구 이용료(1,500,000원) 등 실비성 지출 비중이 커 총액 10,000,000원 안에서는 위 요율을 적용할 수 없다. 2025년과 동일한 요율을 적용할 경우 필요한 총액은 11,286,880원이다. (참고 시트)</t>
+          <t>※ 창업 특강 강사료는 발주처 「강사수당 지급기준」 나급을 적용하였다(강사수당 지급기준 시트 참조).  ※ 2025년 원가계산서는 일반관리비 6% · 이윤 10%를 적용하였으나, 본 과업은 시상금(2,500,000원)과 AI 코딩 도구 이용료(1,500,000원) 등 실비성 지출 비중이 커 총액 10,000,000원 안에서는 위 요율을 적용할 수 없다. 2025년과 동일한 요율을 적용할 경우 필요한 총액은 11,036,880원이다. (참고 시트)</t>
         </is>
       </c>
     </row>
@@ -876,11 +908,11 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>창업 특강 강사료 (나급 상당)</t>
+          <t>창업 특강 강사료 (나급)</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>500000</v>
+        <v>250000</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>1</v>
@@ -894,7 +926,7 @@
       </c>
       <c r="G4" s="24" t="inlineStr">
         <is>
-          <t>9.28(월) 바이브 코딩 실습 특강 2시간</t>
+          <t>9.28(월) 특강 2시간 — 최초 1h 170,000 + 초과 1h 80,000</t>
         </is>
       </c>
     </row>
@@ -1516,10 +1548,10 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>3500000</v>
+        <v>3250000</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>3500000</v>
+        <v>3250000</v>
       </c>
       <c r="D4" s="24" t="inlineStr">
         <is>
@@ -1552,14 +1584,14 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>176000</v>
+        <v>256500</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>528000</v>
+        <v>513000</v>
       </c>
       <c r="D6" s="24" t="inlineStr">
         <is>
-          <t>2.0% → 6.0%</t>
+          <t>3.0% → 6.0%</t>
         </is>
       </c>
     </row>
@@ -1570,14 +1602,14 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>114909</v>
+        <v>284409</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>932800</v>
+        <v>906300</v>
       </c>
       <c r="D7" s="24" t="inlineStr">
         <is>
-          <t>1.28% → 10.0%</t>
+          <t>3.23% → 10.0%</t>
         </is>
       </c>
     </row>
@@ -1591,7 +1623,7 @@
         <v>9090909</v>
       </c>
       <c r="C8" s="10" t="n">
-        <v>10260800</v>
+        <v>9969300</v>
       </c>
       <c r="D8" s="26" t="inlineStr"/>
     </row>
@@ -1605,7 +1637,7 @@
         <v>909091</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1026080</v>
+        <v>996930</v>
       </c>
       <c r="D9" s="24" t="inlineStr"/>
     </row>
@@ -1619,18 +1651,18 @@
         <v>10000000</v>
       </c>
       <c r="C10" s="19" t="n">
-        <v>11286880</v>
+        <v>10966230</v>
       </c>
       <c r="D10" s="21" t="inlineStr">
         <is>
-          <t>차액 1,286,880원</t>
+          <t>차액 966,230원</t>
         </is>
       </c>
     </row>
     <row r="12" ht="40" customHeight="1">
       <c r="A12" s="22" t="inlineStr">
         <is>
-          <t>※ 2025년 예산은 13,000,000원이었고 시상금이 없었다. 2026년은 총액이 10,000,000원으로 줄어든 대신 경진대회와 시상금 2,500,000원이 새로 들어갔다. 요율을 지키려면 총액 11,286,880원(천원 단위 절상 시 11,290,000원)이 필요하다.</t>
+          <t>※ 2025년 예산은 13,000,000원이었고 시상금이 없었다. 2026년은 총액이 10,000,000원으로 줄어든 대신 경진대회와 시상금 2,500,000원이 새로 들어갔다. 요율을 지키려면 총액 11,036,880원(천원 단위 절상 시 11,040,000원)이 필요하다.</t>
         </is>
       </c>
     </row>
@@ -1641,4 +1673,231 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>강사수당 지급기준 — 가. 일반강의 강사수당</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>단위 : 원</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>등급</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>적용대상 (일반)</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>최초 1시간</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>초과 매시간</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>2시간 환산</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="27" t="inlineStr">
+        <is>
+          <t>특1급</t>
+        </is>
+      </c>
+      <c r="B4" s="28" t="inlineStr">
+        <is>
+          <t>전직 장관(급) 및 광역자치단체장, 전직 국회의원, 전직 한국은행장, 전직 대학의 총장(이사장), 대기업 총수(부회장 이상)</t>
+        </is>
+      </c>
+      <c r="C4" s="29" t="n">
+        <v>400000</v>
+      </c>
+      <c r="D4" s="29" t="n">
+        <v>300000</v>
+      </c>
+      <c r="E4" s="29">
+        <f>C4+D4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>특2급</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>전직 차관(급) 및 기초자치단체장, 전직 공직유관단체장, 전직 전문대학 등의 총장(이사장), 대기업 임원·중견기업 대표</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>200000</v>
+      </c>
+      <c r="E5" s="5">
+        <f>C5+D5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="27" t="inlineStr">
+        <is>
+          <t>가급</t>
+        </is>
+      </c>
+      <c r="B6" s="28" t="inlineStr">
+        <is>
+          <t>전직 4급 이상 공무원, 전직 대학의 교수(조교수 이상), 대기업 부장(급)·중견기업 임원·중소기업 대표, 전문직 3년 이상, 박사학위 취득 후 해당분야 3년 이상 실무경력자</t>
+        </is>
+      </c>
+      <c r="C6" s="29" t="n">
+        <v>280000</v>
+      </c>
+      <c r="D6" s="29" t="n">
+        <v>120000</v>
+      </c>
+      <c r="E6" s="29">
+        <f>C6+D6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="30" t="inlineStr">
+        <is>
+          <t>나급</t>
+        </is>
+      </c>
+      <c r="B7" s="31" t="inlineStr">
+        <is>
+          <t>전직 5급(상당) 공무원, 중견기업 부장(급)·중소기업 임원, 국가전문자격증 보유 3년 이상 실무경력자, 기타 전문자격 보유 5년 이상 실무경력자</t>
+        </is>
+      </c>
+      <c r="C7" s="32" t="n">
+        <v>170000</v>
+      </c>
+      <c r="D7" s="32" t="n">
+        <v>80000</v>
+      </c>
+      <c r="E7" s="33">
+        <f>C7+D7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="27" t="inlineStr">
+        <is>
+          <t>다급</t>
+        </is>
+      </c>
+      <c r="B8" s="28" t="inlineStr">
+        <is>
+          <t>전직 6급 이하 공무원, 외국어·전산 등 강사, 체육·레크리에이션 등 취미·소양 강사(해당분야 3년 이상 강의경력)</t>
+        </is>
+      </c>
+      <c r="C8" s="29" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D8" s="29" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E8" s="29">
+        <f>C8+D8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>라급</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>체육, 레크리에이션 등 취미·소양 강사</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>80000</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="E9" s="5">
+        <f>C9+D9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="27" t="inlineStr">
+        <is>
+          <t>마급</t>
+        </is>
+      </c>
+      <c r="B10" s="28" t="inlineStr">
+        <is>
+          <t>각종 교육운영(실기실습 등) 보조자</t>
+        </is>
+      </c>
+      <c r="C10" s="29" t="n">
+        <v>60000</v>
+      </c>
+      <c r="D10" s="29" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E10" s="29">
+        <f>C10+D10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="46" customHeight="1">
+      <c r="A12" s="22" t="inlineStr">
+        <is>
+          <t>※ 본 과업의 창업 특강(2시간)은 나급을 적용하여 170,000 + 80,000 = 250,000원으로 계상하였다. 2025년 원가계산서도 동일하게 나급을 적용하였다 (4시간 17+8+8+8 = 410,000원, 3시간 17+8+8 = 330,000원). 강사가 중소기업 대표 등 가급 요건에 해당하면 2시간 400,000원까지 적용할 수 있다.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A12:E12"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/2026-계획안-견적서/2026_바이브코딩_특강및경진대회_원가계산서.xlsx
+++ b/docs/2026-계획안-견적서/2026_바이브코딩_특강및경진대회_원가계산서.xlsx
@@ -23,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -77,6 +77,11 @@
       <color rgb="00000000"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -111,7 +116,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -133,11 +138,77 @@
         <color rgb="009AA5B1"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="009AA5B1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="009AA5B1"/>
+      </right>
+      <top style="thin">
+        <color rgb="009AA5B1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="009AA5B1"/>
+      </right>
+      <top style="thin">
+        <color rgb="009AA5B1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="009AA5B1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="009AA5B1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="009AA5B1"/>
+      </left>
+      <right style="thin">
+        <color rgb="009AA5B1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="009AA5B1"/>
+      </left>
+      <right style="thin">
+        <color rgb="009AA5B1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="009AA5B1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -217,10 +288,15 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -229,7 +305,7 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1681,27 +1757,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="54" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="23" t="inlineStr">
         <is>
-          <t>강사수당 지급기준 — 가. 일반강의 강사수당</t>
+          <t>3. 강사수당 지급기준 —  가. 일반강의 강사수당</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>단위 : 원</t>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(단위 : 원)</t>
         </is>
       </c>
     </row>
@@ -1713,190 +1790,304 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>적용대상 (일반)</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
+          <t>적용대상 (청탁금지법 적용 유무로 구분)</t>
+        </is>
+      </c>
+      <c r="C3" s="27" t="n"/>
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>최초 1시간</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>초과 매시간</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>2시간 환산</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="27" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="28" t="n"/>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>공직자 등</t>
+        </is>
+      </c>
+      <c r="D4" s="28" t="n"/>
+      <c r="E4" s="28" t="n"/>
+      <c r="F4" s="28" t="n"/>
+    </row>
+    <row r="5" ht="55" customHeight="1">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>특1급</t>
         </is>
       </c>
-      <c r="B4" s="28" t="inlineStr">
-        <is>
-          <t>전직 장관(급) 및 광역자치단체장, 전직 국회의원, 전직 한국은행장, 전직 대학의 총장(이사장), 대기업 총수(부회장 이상)</t>
-        </is>
-      </c>
-      <c r="C4" s="29" t="n">
+      <c r="B5" s="29" t="inlineStr">
+        <is>
+          <t>• 전직 장관(급) 및 광역자치단체장
+• 전직 국회의원
+• 전직 한국은행장
+• 전직 대학의 총장(이사장)
+• 대기업 총수(부회장 이상)</t>
+        </is>
+      </c>
+      <c r="C5" s="29" t="inlineStr">
+        <is>
+          <t>• 장관(급)*, 광역자치단체장*
+• 국회의원*
+• 한국은행장*
+• 대학의 총장(이사장)</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n">
         <v>400000</v>
       </c>
-      <c r="D4" s="29" t="n">
+      <c r="E5" s="5" t="n">
         <v>300000</v>
       </c>
-      <c r="E4" s="29">
-        <f>C4+D4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="F5" s="5">
+        <f>D5+E5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="44" customHeight="1">
+      <c r="A6" s="30" t="inlineStr">
         <is>
           <t>특2급</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>전직 차관(급) 및 기초자치단체장, 전직 공직유관단체장, 전직 전문대학 등의 총장(이사장), 대기업 임원·중견기업 대표</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n">
+      <c r="B6" s="31" t="inlineStr">
+        <is>
+          <t>• 전직 차관(급) 및 기초자치단체장
+• 전직 공직유관단체장
+• 전직 전문대학 등의 총장(이사장)
+• 대기업 임원, 중견기업 대표</t>
+        </is>
+      </c>
+      <c r="C6" s="31" t="inlineStr">
+        <is>
+          <t>• 차관(급), 기초자치단체장
+• 공직유관단체장
+• 전문대학 등의 총장(이사장)
+• 대형언론사 총수</t>
+        </is>
+      </c>
+      <c r="D6" s="32" t="n">
         <v>300000</v>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="E6" s="32" t="n">
         <v>200000</v>
       </c>
-      <c r="E5" s="5">
-        <f>C5+D5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="27" t="inlineStr">
+      <c r="F6" s="32">
+        <f>D6+E6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="99" customHeight="1">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>가급</t>
         </is>
       </c>
-      <c r="B6" s="28" t="inlineStr">
-        <is>
-          <t>전직 4급 이상 공무원, 전직 대학의 교수(조교수 이상), 대기업 부장(급)·중견기업 임원·중소기업 대표, 전문직 3년 이상, 박사학위 취득 후 해당분야 3년 이상 실무경력자</t>
-        </is>
-      </c>
-      <c r="C6" s="29" t="n">
+      <c r="B7" s="29" t="inlineStr">
+        <is>
+          <t>• 전직 4급 이상 공무원
+• 전직 지방의회의원(의장 포함)
+• 전직 공직유관단체 임원(출연연구기관 부연구위원 이상)
+• 전직 대학의 교수(조교수 이상)
+• 유명 예술인·종교인, 이와 유사 분야의 유명 인사
+• 대기업 부장(급), 중견기업 임원, 중소기업 대표 (이에 준하는 기관·단체 적용 가능)
+• '전문직'으로서 3년 이상 실무경력자
+• 박사학위 취득 후 해당분야 3년 이상 실무경력자 (취미·소양·외국어·전산 강사 제외)
+• 국가대표 지도자 및 국가대표 출신 강사</t>
+        </is>
+      </c>
+      <c r="C7" s="29" t="inlineStr">
+        <is>
+          <t>• 4급 이상 공무원
+• 지방의회의원(의장 포함)
+• 공직유관단체 임원(출연연구기관 부연구위원 이상)
+• 대학의 교수(조교수 이상)
+• 초·중·고교의 장(이사장)
+• 대형언론사 임원
+• 기타언론사 대표</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n">
         <v>280000</v>
       </c>
-      <c r="D6" s="29" t="n">
+      <c r="E7" s="5" t="n">
         <v>120000</v>
       </c>
-      <c r="E6" s="29">
-        <f>C6+D6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="36" customHeight="1">
-      <c r="A7" s="30" t="inlineStr">
+      <c r="F7" s="5">
+        <f>D7+E7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="55" customHeight="1">
+      <c r="A8" s="33" t="inlineStr">
         <is>
           <t>나급</t>
         </is>
       </c>
-      <c r="B7" s="31" t="inlineStr">
-        <is>
-          <t>전직 5급(상당) 공무원, 중견기업 부장(급)·중소기업 임원, 국가전문자격증 보유 3년 이상 실무경력자, 기타 전문자격 보유 5년 이상 실무경력자</t>
-        </is>
-      </c>
-      <c r="C7" s="32" t="n">
+      <c r="B8" s="34" t="inlineStr">
+        <is>
+          <t>• 전직 5급(상당) 공무원
+• 중견기업 부장(급), 중소기업 임원 (이에 준하는 기관·단체 적용 가능)
+• 원어민 어학 강사(외국국적을 가진 자로서 해당 국가에서 고등교육을 이수한 자)
+• 국가전문자격증을 가진 자로서 3년 이상 실무경력자
+• 기타 전문자격을 가진 자로서 5년 이상 실무경력자</t>
+        </is>
+      </c>
+      <c r="C8" s="34" t="inlineStr">
+        <is>
+          <t>• 5급 이하 공무원
+• 공직유관단체 직원
+• 대학의 강사 등(교직원 포함)
+• 초·중·고교의 교직원
+• 기타언론사 임원</t>
+        </is>
+      </c>
+      <c r="D8" s="35" t="n">
         <v>170000</v>
       </c>
-      <c r="D7" s="32" t="n">
+      <c r="E8" s="35" t="n">
         <v>80000</v>
       </c>
-      <c r="E7" s="33">
-        <f>C7+D7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="36" customHeight="1">
-      <c r="A8" s="27" t="inlineStr">
+      <c r="F8" s="36">
+        <f>D8+E8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="33" customHeight="1">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>다급</t>
         </is>
       </c>
-      <c r="B8" s="28" t="inlineStr">
-        <is>
-          <t>전직 6급 이하 공무원, 외국어·전산 등 강사, 체육·레크리에이션 등 취미·소양 강사(해당분야 3년 이상 강의경력)</t>
-        </is>
-      </c>
-      <c r="C8" s="29" t="n">
+      <c r="B9" s="29" t="inlineStr">
+        <is>
+          <t>• 전직 6급 이하 공무원
+• 외국어, 전산 등 강사
+• 체육, 레크리에이션 등 취미·소양 강사로서 해당분야 3년 이상(공공기관·공공교육훈련기관 경력) 또는 5년 이상(외부경력 포함) 강의 경력자</t>
+        </is>
+      </c>
+      <c r="C9" s="29" t="inlineStr"/>
+      <c r="D9" s="5" t="n">
         <v>100000</v>
       </c>
-      <c r="D8" s="29" t="n">
+      <c r="E9" s="5" t="n">
         <v>50000</v>
       </c>
-      <c r="E8" s="29">
-        <f>C8+D8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="F9" s="5">
+        <f>D9+E9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="30" t="inlineStr">
         <is>
           <t>라급</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>체육, 레크리에이션 등 취미·소양 강사</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="n">
+      <c r="B10" s="31" t="inlineStr">
+        <is>
+          <t>• 체육, 레크리에이션 등 취미·소양 강사</t>
+        </is>
+      </c>
+      <c r="C10" s="31" t="inlineStr"/>
+      <c r="D10" s="32" t="n">
         <v>80000</v>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="E10" s="32" t="n">
         <v>40000</v>
       </c>
-      <c r="E9" s="5">
-        <f>C9+D9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="27" t="inlineStr">
+      <c r="F10" s="32">
+        <f>D10+E10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>마급</t>
         </is>
       </c>
-      <c r="B10" s="28" t="inlineStr">
-        <is>
-          <t>각종 교육운영(실기실습 등) 보조자</t>
-        </is>
-      </c>
-      <c r="C10" s="29" t="n">
+      <c r="B11" s="29" t="inlineStr">
+        <is>
+          <t>• 각종 교육운영(실기실습 등) 보조자</t>
+        </is>
+      </c>
+      <c r="C11" s="29" t="inlineStr"/>
+      <c r="D11" s="5" t="n">
         <v>60000</v>
       </c>
-      <c r="D10" s="29" t="n">
+      <c r="E11" s="5" t="n">
         <v>30000</v>
       </c>
-      <c r="E10" s="29">
-        <f>C10+D10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="46" customHeight="1">
+      <c r="F11" s="5">
+        <f>D11+E11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
       <c r="A12" s="22" t="inlineStr">
         <is>
-          <t>※ 본 과업의 창업 특강(2시간)은 나급을 적용하여 170,000 + 80,000 = 250,000원으로 계상하였다. 2025년 원가계산서도 동일하게 나급을 적용하였다 (4시간 17+8+8+8 = 410,000원, 3시간 17+8+8 = 330,000원). 강사가 중소기업 대표 등 가급 요건에 해당하면 2시간 400,000원까지 적용할 수 있다.</t>
+          <t>1. 전문직 : 감정평가사, 건축사, 공인노무사, 공인회계사, 관세사, 기술사, 법무사, 변리사, 변호사, 보험계리사, 세무사, 약사, 의사</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="22" t="inlineStr">
+        <is>
+          <t>2. 특1급 초과 매시간은 300,000원이나, * 표시된 청탁금지법 적용 대상(공직자 등)은 200,000원을 적용한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="22" t="inlineStr">
+        <is>
+          <t>3. 2시간 환산 = 최초 1시간 + 초과 1시간. 본 과업의 창업 특강(2시간)은 나급을 적용하여 170,000 + 80,000 = 250,000원으로 계상하였다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="22" t="inlineStr">
+        <is>
+          <t>4. 2025년 원가계산서도 동일하게 나급을 적용하였다 (4시간 17+8+8+8 = 410,000원 / 3시간 17+8+8 = 330,000원).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="22" t="inlineStr">
+        <is>
+          <t>5. 강사가 중소기업 대표 등 가급 요건에 해당하면 2시간 400,000원까지 적용할 수 있다.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A12:E12"/>
+  <mergeCells count="11">
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A15:F15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
